--- a/assets/data/排列3历史数据.xlsx
+++ b/assets/data/排列3历史数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7641"/>
+  <dimension ref="A1:D7645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -107410,6 +107410,62 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7642">
+      <c r="A7642" t="n">
+        <v>26166</v>
+      </c>
+      <c r="B7642" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7642" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7642" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7643">
+      <c r="A7643" t="n">
+        <v>26167</v>
+      </c>
+      <c r="B7643" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7643" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7643" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7644">
+      <c r="A7644" t="n">
+        <v>26168</v>
+      </c>
+      <c r="B7644" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7644" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7644" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7645">
+      <c r="A7645" t="n">
+        <v>26169</v>
+      </c>
+      <c r="B7645" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7645" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7645" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/排列3历史数据.xlsx
+++ b/assets/data/排列3历史数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7645"/>
+  <dimension ref="A1:D7647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -107466,6 +107466,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7646">
+      <c r="A7646" t="n">
+        <v>26170</v>
+      </c>
+      <c r="B7646" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7646" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7646" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7647">
+      <c r="A7647" t="n">
+        <v>26171</v>
+      </c>
+      <c r="B7647" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7647" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7647" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
